--- a/docs/开房规则表/扯旋/成都扯旋CD299.xlsx
+++ b/docs/开房规则表/扯旋/成都扯旋CD299.xlsx
@@ -1,318 +1,175 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15900"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="15800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="公共创建规则" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公共创建规则" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
-  <si>
-    <t>省份</t>
-  </si>
-  <si>
-    <t>四川</t>
-  </si>
-  <si>
-    <t>地区名称</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>显示名称</t>
-  </si>
-  <si>
-    <t>扯旋</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>省份和地区仅用于玩法分类；玩法编码 CD299 用于稳定识别，不随显示名称变化。</t>
-  </si>
-  <si>
-    <t>界面显示文字</t>
-  </si>
-  <si>
-    <t>控件类型</t>
-  </si>
-  <si>
-    <t>可选项显示文字</t>
-  </si>
-  <si>
-    <t>默认勾选</t>
-  </si>
-  <si>
-    <t>托管次数</t>
-  </si>
-  <si>
-    <t>是否显示</t>
-  </si>
-  <si>
-    <t>房间时长</t>
-  </si>
-  <si>
-    <t>单选</t>
-  </si>
-  <si>
-    <t>30分钟｜45分钟｜60分钟｜10局｜20局｜30局</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>开局人数</t>
-  </si>
-  <si>
-    <t>2人｜4人｜6人</t>
-  </si>
-  <si>
-    <t>操作时间</t>
-  </si>
-  <si>
-    <t>10秒｜15秒｜30秒</t>
-  </si>
-  <si>
-    <t>站起规则</t>
-  </si>
-  <si>
-    <t>输家可站起｜所有人可站起｜所有人不可站起</t>
-  </si>
-  <si>
-    <t>芒果翻法</t>
-  </si>
-  <si>
-    <t>梯翻｜滚翻</t>
-  </si>
-  <si>
-    <t>升芒</t>
-  </si>
-  <si>
-    <t>不升｜1芒｜2芒｜3芒｜4芒｜5芒</t>
-  </si>
-  <si>
-    <t>分数设置</t>
-  </si>
-  <si>
-    <t>数字</t>
-  </si>
-  <si>
-    <t>芒果分数｜发招分数（发招分数不低于芒果分数）</t>
-  </si>
-  <si>
-    <t>3｜3</t>
-  </si>
-  <si>
-    <t>玩法</t>
-  </si>
-  <si>
-    <t>多选</t>
-  </si>
-  <si>
-    <t>休芒｜揍芒｜手手芒｜首轮可休｜挨家必挨｜地九王｜防火牌｜头大不输底</t>
-  </si>
-  <si>
-    <t>1,2,3,4,6,7</t>
-  </si>
-  <si>
-    <t>房间结束方式</t>
-  </si>
-  <si>
-    <t>按局数 | 按时间</t>
-  </si>
-  <si>
-    <t>房间局数</t>
-  </si>
-  <si>
-    <t>10局</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="23">
     <font>
-      <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color rgb="FF184E72"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <i/>
+      <i val="1"/>
+      <color rgb="FF9C6500"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF222222"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -654,169 +511,169 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1065,7 +922,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1074,7 +931,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1087,11 +944,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1288,306 +1208,367 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="24" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="62" style="1" customWidth="1"/>
-    <col min="4" max="7" width="13" style="1" customWidth="1"/>
+    <col width="24" customWidth="1" style="1" min="1" max="1"/>
+    <col width="14" customWidth="1" style="1" min="2" max="2"/>
+    <col width="62" customWidth="1" style="1" min="3" max="3"/>
+    <col width="13" customWidth="1" style="1" min="4" max="7"/>
+    <col width="13" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13" customWidth="1" style="1" min="6" max="6"/>
+    <col width="13" customWidth="1" style="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" ht="30" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>省份</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="n"/>
+      <c r="D1" s="0" t="n"/>
+      <c r="E1" s="0" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>地区名称</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="n"/>
+      <c r="D2" s="0" t="n"/>
+      <c r="E2" s="0" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>显示名称</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>扯旋</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="n"/>
+      <c r="D3" s="0" t="n"/>
+      <c r="E3" s="0" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="1">
+      <c r="A4" s="0" t="n"/>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="n"/>
+      <c r="D4" s="0" t="n"/>
+      <c r="E4" s="0" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>省份和地区仅用于玩法分类；玩法编码 CD299 用于稳定识别，不随显示名称变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="1">
+      <c r="A6" s="0" t="n"/>
+      <c r="B6" s="0" t="n"/>
+      <c r="C6" s="0" t="n"/>
+      <c r="D6" s="0" t="n"/>
+      <c r="E6" s="0" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>界面显示文字</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>控件类型</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>可选项显示文字</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>默认勾选</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>是否显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>房间时长</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>单选</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>30分钟｜45分钟｜60分钟｜10局｜20局｜30局</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>开局人数</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>单选</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>2人｜4人｜6人</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>操作时间</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>单选</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>10秒｜15秒｜30秒</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>站起规则</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>单选</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>输家可站起｜所有人可站起｜所有人不可站起</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>芒果翻法</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>单选</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>梯翻｜滚翻</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>升芒</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>单选</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>不升｜1芒｜2芒｜3芒｜4芒｜5芒</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A4"/>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>分数设置</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>数字</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>芒果分数｜发招分数（发招分数不低于芒果分数）</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>3｜3</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>玩法</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>多选</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>休芒｜揍芒｜手手芒｜首轮可休｜挨家必挨｜地九王｜防火牌｜头大不输底</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,6,7</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="1">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>托管次数</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>单选</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>3次｜4次｜5次</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="6">
-        <v>3</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
-        <v>3</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6">
-        <v>3</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
-        <v>3</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6">
-        <v>3</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="6">
-        <v>4</v>
-      </c>
-      <c r="E13" s="6">
-        <v>3</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="6">
-        <v>3</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="6">
-        <v>3</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
-      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="1">
+      <c r="A17" s="0" t="n"/>
+      <c r="B17" s="0" t="n"/>
+      <c r="C17" s="0" t="n"/>
+      <c r="D17" s="0" t="n"/>
+      <c r="E17" s="0" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="n"/>
+      <c r="B18" s="0" t="n"/>
+      <c r="C18" s="0" t="n"/>
+      <c r="D18" s="0" t="n"/>
+      <c r="E18" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>